--- a/Excel_luban/Datas/PuzzleMapConfig.xlsx
+++ b/Excel_luban/Datas/PuzzleMapConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -66,27 +66,6 @@
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Type</t>
-    </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -219,6 +198,101 @@
   <si>
     <r>
       <t>ui://PuzzlePKG/map_14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>ui://PuzzlePKG/map_15</t>
+  </si>
+  <si>
+    <r>
+      <t>ui://PuzzlePKG/map_16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>ui://PuzzlePKG/map_17</t>
+  </si>
+  <si>
+    <r>
+      <t>ui://PuzzlePKG/map_18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>ui://PuzzlePKG/map_19</t>
+  </si>
+  <si>
+    <r>
+      <t>ui://PuzzlePKG/map_20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>ui://PuzzlePKG/map_21</t>
+  </si>
+  <si>
+    <r>
+      <t>ui://PuzzlePKG/map_22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>ui://PuzzlePKG/map_23</t>
+  </si>
+  <si>
+    <r>
+      <t>ui://PuzzlePKG/map_24</t>
     </r>
     <r>
       <rPr>
@@ -537,7 +611,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -576,6 +650,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -903,16 +986,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="44.75" customWidth="1"/>
-    <col min="6" max="6" width="20.375" customWidth="1"/>
-    <col min="7" max="7" width="34.875" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="44.75" customWidth="1"/>
+    <col min="5" max="5" width="20.375" customWidth="1"/>
+    <col min="6" max="6" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -920,16 +1003,14 @@
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -948,18 +1029,17 @@
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
       <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-    </row>
-    <row r="2" spans="1:26" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -978,9 +1058,8 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-    </row>
-    <row r="3" spans="1:26" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:25" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -991,13 +1070,11 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -1016,18 +1093,17 @@
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-    </row>
-    <row r="4" spans="1:26" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:25" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -1046,9 +1122,8 @@
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-    </row>
-    <row r="5" spans="1:26" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1056,16 +1131,14 @@
         <v>7</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -1084,23 +1157,20 @@
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-    </row>
-    <row r="6" spans="1:26" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:25" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
       <c r="B6" s="11">
         <v>1001</v>
       </c>
       <c r="C6" s="12">
         <v>1</v>
       </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
@@ -1113,195 +1183,259 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
       <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B7" s="11">
         <v>1002</v>
       </c>
       <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12">
         <v>2</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D7" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B8" s="11">
         <v>1003</v>
       </c>
       <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12">
         <v>3</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D8" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B9" s="11">
         <v>1004</v>
       </c>
       <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="12">
         <v>4</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D9" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B10" s="11">
         <v>1005</v>
       </c>
       <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12">
         <v>5</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D10" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B11" s="11">
         <v>1006</v>
       </c>
       <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12">
         <v>6</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D11" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B12" s="11">
         <v>1007</v>
       </c>
       <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12">
         <v>7</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D12" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B13" s="11">
         <v>1008</v>
       </c>
       <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="12">
         <v>8</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D13" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B14" s="11">
         <v>1009</v>
       </c>
       <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12">
         <v>9</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D14" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B15" s="11">
         <v>1010</v>
       </c>
       <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="12">
         <v>10</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B16" s="18">
+        <v>1011</v>
+      </c>
+      <c r="C16" s="19">
+        <v>11</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="18">
+        <v>1012</v>
+      </c>
+      <c r="C17" s="19">
+        <v>12</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B16" s="11">
-        <v>1011</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="12">
-        <v>11</v>
-      </c>
-      <c r="E16" s="12" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="18">
+        <v>1013</v>
+      </c>
+      <c r="C18" s="19">
+        <v>13</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="11">
-        <v>1012</v>
-      </c>
-      <c r="C17" s="12">
-        <v>1</v>
-      </c>
-      <c r="D17" s="12">
-        <v>12</v>
-      </c>
-      <c r="E17" s="17" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="18">
+        <v>1014</v>
+      </c>
+      <c r="C19" s="19">
+        <v>14</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="11">
-        <v>1013</v>
-      </c>
-      <c r="C18" s="12">
-        <v>1</v>
-      </c>
-      <c r="D18" s="12">
-        <v>13</v>
-      </c>
-      <c r="E18" s="12" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="18">
+        <v>1015</v>
+      </c>
+      <c r="C20" s="19">
+        <v>15</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="11">
-        <v>1014</v>
-      </c>
-      <c r="C19" s="12">
-        <v>1</v>
-      </c>
-      <c r="D19" s="12">
-        <v>14</v>
-      </c>
-      <c r="E19" s="17" t="s">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="18">
+        <v>1016</v>
+      </c>
+      <c r="C21" s="19">
+        <v>16</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="18">
+        <v>1017</v>
+      </c>
+      <c r="C22" s="19">
+        <v>17</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="18">
+        <v>1018</v>
+      </c>
+      <c r="C23" s="19">
+        <v>18</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="18">
+        <v>1019</v>
+      </c>
+      <c r="C24" s="19">
+        <v>19</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="18">
+        <v>1020</v>
+      </c>
+      <c r="C25" s="19">
+        <v>20</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="11">
+        <v>1021</v>
+      </c>
+      <c r="C26" s="12">
+        <v>21</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="11">
+        <v>1022</v>
+      </c>
+      <c r="C27" s="12">
+        <v>22</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="11">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="12">
+        <v>23</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="11">
+        <v>1024</v>
+      </c>
+      <c r="C29" s="12">
+        <v>24</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/Excel_luban/Datas/PuzzleMapConfig.xlsx
+++ b/Excel_luban/Datas/PuzzleMapConfig.xlsx
@@ -61,10 +61,6 @@
     <t>组件</t>
   </si>
   <si>
-    <t>ui://PuzzlePKG/map_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -81,230 +77,79 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>ui://PuzzlePKG/map_0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>ui://Map_10/map</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>ui://PuzzlePKG/map_03</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_05</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_07</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_09</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_11</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_13</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_15</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_17</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_19</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_21</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>ui://PuzzlePKG/map_23</t>
-  </si>
-  <si>
-    <r>
-      <t>ui://PuzzlePKG/map_24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
+    <t>ui://Map_01/map</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui://Map_02/map</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>ui://Map_03/map</t>
+  </si>
+  <si>
+    <t>ui://Map_04/map</t>
+  </si>
+  <si>
+    <t>ui://Map_05/map</t>
+  </si>
+  <si>
+    <t>ui://Map_06/map</t>
+  </si>
+  <si>
+    <t>ui://Map_07/map</t>
+  </si>
+  <si>
+    <t>ui://Map_08/map</t>
+  </si>
+  <si>
+    <t>ui://Map_09/map</t>
+  </si>
+  <si>
+    <t>ui://Map_11/map</t>
+  </si>
+  <si>
+    <t>ui://Map_12/map</t>
+  </si>
+  <si>
+    <t>ui://Map_13/map</t>
+  </si>
+  <si>
+    <t>ui://Map_14/map</t>
+  </si>
+  <si>
+    <t>ui://Map_15/map</t>
+  </si>
+  <si>
+    <t>ui://Map_16/map</t>
+  </si>
+  <si>
+    <t>ui://Map_17/map</t>
+  </si>
+  <si>
+    <t>ui://Map_18/map</t>
+  </si>
+  <si>
+    <t>ui://Map_19/map</t>
+  </si>
+  <si>
+    <t>ui://Map_20/map</t>
+  </si>
+  <si>
+    <t>ui://Map_21/map</t>
+  </si>
+  <si>
+    <t>ui://Map_22/map</t>
+  </si>
+  <si>
+    <t>ui://Map_23/map</t>
+  </si>
+  <si>
+    <t>ui://Map_24/map</t>
   </si>
 </sst>
 </file>
@@ -402,7 +247,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,12 +269,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,6 +398,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -574,7 +416,7 @@
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -590,9 +432,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -604,14 +443,14 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -622,11 +461,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -638,12 +473,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -986,454 +815,422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="44.75" customWidth="1"/>
-    <col min="5" max="5" width="20.375" customWidth="1"/>
-    <col min="6" max="6" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5"/>
+      <c r="C1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+    </row>
+    <row r="2" spans="1:20" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-    </row>
-    <row r="3" spans="1:25" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="9" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+    </row>
+    <row r="3" spans="1:20" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A4" s="9" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="1:20" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>12</v>
+      <c r="C5" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6" spans="1:25" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="B6" s="11">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:20" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B6" s="9">
         <v>1001</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B7" s="9">
+        <v>1002</v>
+      </c>
+      <c r="C7" s="10">
+        <v>2</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B8" s="9">
+        <v>1003</v>
+      </c>
+      <c r="C8" s="10">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="9">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B10" s="9">
+        <v>1005</v>
+      </c>
+      <c r="C10" s="10">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="9">
+        <v>1006</v>
+      </c>
+      <c r="C11" s="10">
+        <v>6</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B12" s="9">
+        <v>1007</v>
+      </c>
+      <c r="C12" s="10">
+        <v>7</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B13" s="9">
+        <v>1008</v>
+      </c>
+      <c r="C13" s="10">
+        <v>8</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B14" s="9">
+        <v>1009</v>
+      </c>
+      <c r="C14" s="10">
         <v>9</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B7" s="11">
-        <v>1002</v>
-      </c>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="D14" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="9">
+        <v>1010</v>
+      </c>
+      <c r="C15" s="10">
+        <v>10</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="B16" s="14">
+        <v>1011</v>
+      </c>
+      <c r="C16" s="15">
+        <v>11</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="14">
+        <v>1012</v>
+      </c>
+      <c r="C17" s="15">
+        <v>12</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="14">
+        <v>1013</v>
+      </c>
+      <c r="C18" s="15">
+        <v>13</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="14">
+        <v>1014</v>
+      </c>
+      <c r="C19" s="15">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B8" s="11">
-        <v>1003</v>
-      </c>
-      <c r="C8" s="12">
-        <v>3</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="D19" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="14">
+        <v>1015</v>
+      </c>
+      <c r="C20" s="15">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B9" s="11">
-        <v>1004</v>
-      </c>
-      <c r="C9" s="12">
-        <v>4</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="D20" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="14">
+        <v>1016</v>
+      </c>
+      <c r="C21" s="15">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B10" s="11">
-        <v>1005</v>
-      </c>
-      <c r="C10" s="12">
-        <v>5</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="D21" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="14">
+        <v>1017</v>
+      </c>
+      <c r="C22" s="15">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B11" s="11">
-        <v>1006</v>
-      </c>
-      <c r="C11" s="12">
-        <v>6</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="D22" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="14">
+        <v>1018</v>
+      </c>
+      <c r="C23" s="15">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B12" s="11">
-        <v>1007</v>
-      </c>
-      <c r="C12" s="12">
-        <v>7</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="D23" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="14">
+        <v>1019</v>
+      </c>
+      <c r="C24" s="15">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B13" s="11">
-        <v>1008</v>
-      </c>
-      <c r="C13" s="12">
-        <v>8</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="D24" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="14">
+        <v>1020</v>
+      </c>
+      <c r="C25" s="15">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B14" s="11">
-        <v>1009</v>
-      </c>
-      <c r="C14" s="12">
-        <v>9</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="D25" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="9">
+        <v>1021</v>
+      </c>
+      <c r="C26" s="10">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B15" s="11">
-        <v>1010</v>
-      </c>
-      <c r="C15" s="12">
-        <v>10</v>
-      </c>
-      <c r="D15" s="17" t="s">
+      <c r="D26" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="9">
+        <v>1022</v>
+      </c>
+      <c r="C27" s="10">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B16" s="18">
-        <v>1011</v>
-      </c>
-      <c r="C16" s="19">
-        <v>11</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="D27" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="9">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="10">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="18">
-        <v>1012</v>
-      </c>
-      <c r="C17" s="19">
-        <v>12</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="D28" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="9">
+        <v>1024</v>
+      </c>
+      <c r="C29" s="10">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="18">
-        <v>1013</v>
-      </c>
-      <c r="C18" s="19">
-        <v>13</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="18">
-        <v>1014</v>
-      </c>
-      <c r="C19" s="19">
-        <v>14</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="18">
-        <v>1015</v>
-      </c>
-      <c r="C20" s="19">
-        <v>15</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="18">
-        <v>1016</v>
-      </c>
-      <c r="C21" s="19">
-        <v>16</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="18">
-        <v>1017</v>
-      </c>
-      <c r="C22" s="19">
-        <v>17</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="18">
-        <v>1018</v>
-      </c>
-      <c r="C23" s="19">
-        <v>18</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="18">
-        <v>1019</v>
-      </c>
-      <c r="C24" s="19">
-        <v>19</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="18">
-        <v>1020</v>
-      </c>
-      <c r="C25" s="19">
-        <v>20</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="11">
-        <v>1021</v>
-      </c>
-      <c r="C26" s="12">
-        <v>21</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="11">
-        <v>1022</v>
-      </c>
-      <c r="C27" s="12">
-        <v>22</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="11">
-        <v>1023</v>
-      </c>
-      <c r="C28" s="12">
-        <v>23</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="11">
-        <v>1024</v>
-      </c>
-      <c r="C29" s="12">
-        <v>24</v>
-      </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="13" t="s">
         <v>36</v>
       </c>
     </row>

--- a/Excel_luban/Datas/PuzzleMapConfig.xlsx
+++ b/Excel_luban/Datas/PuzzleMapConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +150,36 @@
   </si>
   <si>
     <t>ui://Map_24/map</t>
+  </si>
+  <si>
+    <t>ui://Map_25/map</t>
+  </si>
+  <si>
+    <t>ui://Map_26/map</t>
+  </si>
+  <si>
+    <t>ui://Map_27/map</t>
+  </si>
+  <si>
+    <t>ui://Map_28/map</t>
+  </si>
+  <si>
+    <t>ui://Map_29/map</t>
+  </si>
+  <si>
+    <t>ui://Map_30/map</t>
+  </si>
+  <si>
+    <t>ui://Map_31/map</t>
+  </si>
+  <si>
+    <t>ui://Map_32/map</t>
+  </si>
+  <si>
+    <t>ui://Map_33/map</t>
+  </si>
+  <si>
+    <t>ui://Map_34/map</t>
   </si>
 </sst>
 </file>
@@ -450,7 +480,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -490,6 +520,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="3"/>
@@ -815,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="25" customWidth="1"/>
@@ -1234,6 +1265,116 @@
         <v>36</v>
       </c>
     </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="9">
+        <v>1025</v>
+      </c>
+      <c r="C30" s="10">
+        <v>25</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="9">
+        <v>1026</v>
+      </c>
+      <c r="C31" s="10">
+        <v>26</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="9">
+        <v>1027</v>
+      </c>
+      <c r="C32" s="10">
+        <v>27</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="9">
+        <v>1028</v>
+      </c>
+      <c r="C33" s="10">
+        <v>28</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="9">
+        <v>1029</v>
+      </c>
+      <c r="C34" s="10">
+        <v>29</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="9">
+        <v>1030</v>
+      </c>
+      <c r="C35" s="10">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="14">
+        <v>1031</v>
+      </c>
+      <c r="C36" s="15">
+        <v>31</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="14">
+        <v>1032</v>
+      </c>
+      <c r="C37" s="15">
+        <v>32</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="14">
+        <v>1033</v>
+      </c>
+      <c r="C38" s="15">
+        <v>33</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="14">
+        <v>1034</v>
+      </c>
+      <c r="C39" s="15">
+        <v>34</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
